--- a/港岛-铜锣湾-宏丰台10号/宏丰台10号_销控明细表.xlsx
+++ b/港岛-铜锣湾-宏丰台10号/宏丰台10号_销控明细表.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
   <fonts count="18">
     <font>
       <name val="Calibri"/>
@@ -114,7 +116,7 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -194,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -208,6 +210,9 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -253,7 +258,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -630,8 +635,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -745,23 +750,19 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>190000000</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1104651</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -815,23 +816,19 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>190000000</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>763052</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -885,23 +882,19 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>190000000</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>926829</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -955,23 +948,19 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>190000000</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>260274</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -1025,23 +1014,19 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>190000000</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>45476</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1095,23 +1080,19 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>190000000</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>43201</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1167,193 +1148,193 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>宏丰台10号 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr"/>
-      <c r="C5" s="19" t="inlineStr"/>
-      <c r="D5" s="19" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
+$19000万
+$926,829/呎
+(26年-08月-04日)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>E | 249呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
+$19000万
+$763,052/呎
+(26年-08月-04日)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>F | 172呎 (开放式)
--
--
-(待售)</t>
+$19000万
+$1,104,651/呎
+(26年-08月-04日)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>G&amp;2</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr"/>
-      <c r="C6" s="19" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 730呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="inlineStr"/>
-      <c r="F6" s="19" t="inlineStr"/>
-      <c r="G6" s="19" t="inlineStr"/>
+$19000万
+$260,274/呎
+(26年-08月-04日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>G&amp;1-3</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 4398呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
+$19000万
+$43,201/呎
+(26年-08月-04日)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 4178呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr"/>
-      <c r="E7" s="19" t="inlineStr"/>
-      <c r="F7" s="19" t="inlineStr"/>
-      <c r="G7" s="19" t="inlineStr"/>
+$19000万
+$45,476/呎
+(26年-08月-04日)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
